--- a/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/model_summary.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/model_summary.xlsx
@@ -497,31 +497,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.96</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07612244897959183</v>
+        <v>0.035</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9263157894736842</v>
+        <v>0.7875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03696720615036048</v>
+        <v>0.06468406123441676</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.9525</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="3">
@@ -536,31 +536,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02777777777777777</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8892857142857142</v>
+        <v>0.9941176470588236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02789374884252377</v>
+        <v>0.04423731048109208</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8711111111111112</v>
+        <v>0.8055555555555556</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7422222222222222</v>
+        <v>0.638888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6875</v>
       </c>
       <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.1258271604938271</v>
+        <v>0.05827362996480642</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9142857142857144</v>
+        <v>1.21764705882353</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02564364193873573</v>
+        <v>0.04300335725384571</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6935849775240639</v>
+        <v>0.7415967700971651</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4476293699711734</v>
+        <v>0.4831935401943302</v>
       </c>
     </row>
     <row r="5">
@@ -617,22 +617,22 @@
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.015</v>
+        <v>0.05823558897243111</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8612903225806452</v>
+        <v>1.052631578947369</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04638635400026451</v>
+        <v>0.04574878880843965</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>

--- a/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/model_summary.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelCompar/tables/model_summary.xlsx
@@ -497,31 +497,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.96</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.035</v>
+        <v>0.1431597076758367</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7875</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06468406123441676</v>
+        <v>0.01960784313725491</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9525</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K2" t="n">
-        <v>0.905</v>
+        <v>0.3809523809523809</v>
       </c>
     </row>
     <row r="3">
@@ -539,28 +539,28 @@
         <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.05827362996480642</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9941176470588236</v>
+        <v>1.041176470588235</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04423731048109208</v>
+        <v>0.06203643929237794</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="K3" t="n">
-        <v>0.638888888888889</v>
+        <v>0.5384615384615385</v>
       </c>
     </row>
     <row r="4">
@@ -581,25 +581,25 @@
         <v>0.6875</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05827362996480642</v>
+        <v>0.1282273860398861</v>
       </c>
       <c r="H4" t="n">
-        <v>1.21764705882353</v>
+        <v>1.088235294117647</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04300335725384571</v>
+        <v>0.02666955001712832</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7415967700971651</v>
+        <v>0.6641892707670098</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4831935401943302</v>
+        <v>0.4421542359796504</v>
       </c>
     </row>
     <row r="5">
@@ -617,22 +617,22 @@
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05823558897243111</v>
+        <v>0.06955070603337615</v>
       </c>
       <c r="H5" t="n">
-        <v>1.052631578947369</v>
+        <v>1.042105263157895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04574878880843965</v>
+        <v>0.04493420517496737</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
